--- a/experiments/results/resnet34/CIFAR-100/ReAct+DICE/adaptive/std/results.xlsx
+++ b/experiments/results/resnet34/CIFAR-100/ReAct+DICE/adaptive/std/results.xlsx
@@ -353,7 +353,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O6"/>
+  <dimension ref="A1:O9"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="61.33203125" customWidth="1" style="3" min="15" max="15"/>
@@ -666,6 +666,153 @@
       <c r="O6" s="5" t="inlineStr">
         <is>
           <t>dice_p=85,ash_p=None,react_th=1.5,scale_th=1.5,type=std</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="n">
+        <v>11.14</v>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>97.66</v>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>91.51000000000001</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>64.95999999999999</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>68.76000000000001</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>85.45</v>
+      </c>
+      <c r="G7" s="5" t="n">
+        <v>36.12</v>
+      </c>
+      <c r="H7" s="5" t="n">
+        <v>90.34</v>
+      </c>
+      <c r="I7" s="5" t="n">
+        <v>13.41</v>
+      </c>
+      <c r="J7" s="5" t="n">
+        <v>97.53</v>
+      </c>
+      <c r="K7" s="5" t="n">
+        <v>75.73999999999999</v>
+      </c>
+      <c r="L7" s="5" t="n">
+        <v>83.28</v>
+      </c>
+      <c r="M7" s="5" t="n">
+        <v>49.45</v>
+      </c>
+      <c r="N7" s="5" t="n">
+        <v>86.54000000000001</v>
+      </c>
+      <c r="O7" s="5" t="inlineStr">
+        <is>
+          <t>dice_p=85,ash_p=None,react_th=1.5,scale_th=3.0,type=std</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="n">
+        <v>19.7</v>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>96.14</v>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>94.65000000000001</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>57.93</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>81.31999999999999</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>79.41</v>
+      </c>
+      <c r="G8" s="5" t="n">
+        <v>41.03</v>
+      </c>
+      <c r="H8" s="5" t="n">
+        <v>87.73</v>
+      </c>
+      <c r="I8" s="5" t="n">
+        <v>22.98</v>
+      </c>
+      <c r="J8" s="5" t="n">
+        <v>95.64</v>
+      </c>
+      <c r="K8" s="5" t="n">
+        <v>87.25</v>
+      </c>
+      <c r="L8" s="5" t="n">
+        <v>76.34</v>
+      </c>
+      <c r="M8" s="5" t="n">
+        <v>57.82</v>
+      </c>
+      <c r="N8" s="5" t="n">
+        <v>82.2</v>
+      </c>
+      <c r="O8" s="5" t="inlineStr">
+        <is>
+          <t>dice_p=85,ash_p=None,react_th=1.0,scale_th=3.0,type=std</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="n">
+        <v>11.14</v>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>97.66</v>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>91.51000000000001</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>64.95999999999999</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>68.76000000000001</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>85.45</v>
+      </c>
+      <c r="G9" s="5" t="n">
+        <v>36.12</v>
+      </c>
+      <c r="H9" s="5" t="n">
+        <v>90.34</v>
+      </c>
+      <c r="I9" s="5" t="n">
+        <v>13.41</v>
+      </c>
+      <c r="J9" s="5" t="n">
+        <v>97.53</v>
+      </c>
+      <c r="K9" s="5" t="n">
+        <v>75.73999999999999</v>
+      </c>
+      <c r="L9" s="5" t="n">
+        <v>83.28</v>
+      </c>
+      <c r="M9" s="5" t="n">
+        <v>49.45</v>
+      </c>
+      <c r="N9" s="5" t="n">
+        <v>86.54000000000001</v>
+      </c>
+      <c r="O9" s="5" t="inlineStr">
+        <is>
+          <t>dice_p=85,ash_p=None,react_th=1.5,scale_th=3.0,type=std</t>
         </is>
       </c>
     </row>
